--- a/02_Zero_Shot/outputs/Embedding/RoBERTa-base/RESULT_f-droid_roberta-base_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/Embedding/RoBERTa-base/RESULT_f-droid_roberta-base_zeroshot.xlsx
@@ -48796,7 +48796,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6560517770479126</v>
+        <v>0.6560517770479127</v>
       </c>
     </row>
     <row r="4">
@@ -48806,7 +48806,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6553813762226307</v>
+        <v>0.6553813762226308</v>
       </c>
     </row>
     <row r="5">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.742763654000555</v>
+        <v>25.87180673300099</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003429343067230044</v>
+        <v>0.009106584559310451</v>
       </c>
     </row>
   </sheetData>
